--- a/AAII_Financials/Quarterly/ULTA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ULTA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
   <si>
     <t>ULTA</t>
   </si>
@@ -656,533 +656,559 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44044</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43953</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43862</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43771</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43680</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43589</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43498</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43407</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43316</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43134</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43036</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42945</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42854</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42763</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3035700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3163900</v>
+      </c>
+      <c r="F8" s="3">
         <v>3898400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2857600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2788500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2848400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3487600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2530100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2552100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2725800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3554300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2488900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2529800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2634300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3226800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2338800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2297100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2345900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2729400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1995800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1967200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1938500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2198700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1552000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1228000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1173200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2305900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1682500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1666600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1743000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2124700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>1560000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>1488200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>1543700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>1937600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>1342200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>1289900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>1314900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>1580600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>1131200</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1848700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1896200</v>
+      </c>
+      <c r="F9" s="3">
         <v>1925200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1702000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1696800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1734100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1708600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1524500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1573900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1656100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1780800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1496900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1536200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1579400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2014300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1376000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1368900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1404900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1702100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1206300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1169200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1184700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1427700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1006500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>899000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>869600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1499000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1059100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1060700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1098200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1383900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>987700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>952800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>983000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>1279200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>849100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>820500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>838900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>1035700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>704200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1187000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1267600</v>
+      </c>
+      <c r="F10" s="3">
         <v>1973200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1155700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1091700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1114200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1779000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1005600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>978200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1069800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1773500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>992100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>993600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1054900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1212500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>962800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>928200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>941000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1027300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>789500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>798000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>753800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>771000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>545500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>329000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>303600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>806900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>623400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>605900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>644800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>740800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>572300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>535400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>560700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>658400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>493100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>469400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>476000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>544900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>427000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1224,44 +1250,46 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>900</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1343,8 +1371,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1462,8 +1496,14 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1503,48 +1543,48 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>30400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>23600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>40800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>19500</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1557,11 +1597,11 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1581,53 +1621,59 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>81400</v>
+      </c>
+      <c r="F15" s="3">
         <v>81600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>75800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>71200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>72000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>69700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>67000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>65300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>64700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>61700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>61400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>61900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>57900</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1700,8 +1746,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,246 +1792,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2656000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2715600</v>
+      </c>
+      <c r="F17" s="3">
         <v>3421400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2548200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2443600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2446600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2971300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2211600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2222900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2324900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3037200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2161700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2138200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2192200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2779200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1976900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1905700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1908200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2353800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1711500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1634900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1633200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1974400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1450800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1215300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1274700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2018200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1514700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1458600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1505500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1843500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1390800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>1294400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1333800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>1683200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>1179500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>1110100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1126500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>1356300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>991600</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>379600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>448300</v>
+      </c>
+      <c r="F18" s="3">
         <v>476900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>309400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>344900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>401800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>516300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>318500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>329200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>400900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>517100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>327200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>391600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>442100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>447600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>361900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>391400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>437700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>375600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>284300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>332300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>305300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>224300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>101200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>12700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-101500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>287700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>167800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>208000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>237500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>281200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>169200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>193800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>209900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>254400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>162700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>179800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>188400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>224300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>139600</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2021,29 +2087,31 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
@@ -2062,220 +2130,232 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-500</v>
       </c>
       <c r="U20" s="3">
         <v>-400</v>
       </c>
       <c r="V20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-2600</v>
       </c>
       <c r="AA20" s="3">
         <v>-1300</v>
       </c>
       <c r="AB20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>2100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1300</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>1200</v>
       </c>
       <c r="AI20" s="3">
         <v>1300</v>
       </c>
       <c r="AJ20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AL20" s="3">
         <v>400</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>300</v>
-      </c>
-      <c r="AL20" s="3">
-        <v>500</v>
       </c>
       <c r="AM20" s="3">
         <v>300</v>
       </c>
       <c r="AN20" s="3">
+        <v>500</v>
+      </c>
+      <c r="AO20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AP20" s="3">
         <v>100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>458900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>528100</v>
+      </c>
+      <c r="F21" s="3">
         <v>556900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>384200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>415400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>473200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>586000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>385500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>394500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>465700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>578800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>388600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>453600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>500000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>511200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>421200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>452400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>500100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>438900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>349000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>400900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>375600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>295200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>172300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>87500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>364600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>242900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>282800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>311400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>354300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>240400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>264000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>280000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>319800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>225100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>243500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>251200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>283600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>193300</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
         <v>1800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>4100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2300,11 +2380,11 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2378,246 +2458,264 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>373900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>447300</v>
+      </c>
+      <c r="F23" s="3">
         <v>472700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>304300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>345700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>404700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>518300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>320200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>333700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>407800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>520400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>329700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>396100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>449400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>452000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>362700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>391500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>437300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>375200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>283800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>331900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>305000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>223800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>99900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>10100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-102800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>288200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>168700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>209700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>239600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>282500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>170500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>195000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>211200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>254800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>163000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>180400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>188700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>224300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>139900</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>106900</v>
+      </c>
+      <c r="F24" s="3">
         <v>116000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>73400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>84800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>99600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>125000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>78000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>81200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>94700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>126000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>80200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>96000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>102400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>111200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>88100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>95900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>105900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>85800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>68500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>81000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>74700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>52300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>25100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>2100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-24200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>65500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>38900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>48400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>47400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>67800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>39400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>46600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>46800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>8300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>58300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>66200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>60500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>84100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2735,246 +2833,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>340500</v>
+      </c>
+      <c r="F26" s="3">
         <v>356700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>230900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>260900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>305100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>393300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>242200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>252600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>313100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>394400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>249500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>300100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>347100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>340800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>274600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>295700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>331400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>289400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>215300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>250900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>230300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>171500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>74800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>8100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-78500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>222700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>129700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>161300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>192200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>214700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>131200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>148300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>164400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>246500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>104600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>114200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>128200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>140200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>340500</v>
+      </c>
+      <c r="F27" s="3">
         <v>356700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>230900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>260900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>305100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>393300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>242200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>252600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>313100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>394400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>249500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>300100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>347100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>340800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>274600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>295700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>331400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>289400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>215300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>250900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>230300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>171500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>74800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>8100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-78500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>222700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>129700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>161300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>192200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>214700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>131200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>148300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>164400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>246500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>104600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>114200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>128200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>140200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3092,8 +3208,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3175,11 +3297,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3193,15 +3315,15 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-38300</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3211,8 +3333,14 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3330,8 +3458,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3449,29 +3583,35 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3490,205 +3630,217 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>500</v>
       </c>
       <c r="U32" s="3">
         <v>400</v>
       </c>
       <c r="V32" s="3">
+        <v>500</v>
+      </c>
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>2600</v>
       </c>
       <c r="AA32" s="3">
         <v>1300</v>
       </c>
       <c r="AB32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-1200</v>
       </c>
       <c r="AI32" s="3">
         <v>-1300</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AL32" s="3">
-        <v>-500</v>
       </c>
       <c r="AM32" s="3">
         <v>-300</v>
       </c>
       <c r="AN32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AO32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AP32" s="3">
         <v>-100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>340500</v>
+      </c>
+      <c r="F33" s="3">
         <v>356700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>230900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>260900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>305100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>393300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>242200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>252600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>313100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>394400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>249500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>300100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>347100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>340800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>274600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>295700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>331400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>289400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>215300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>250900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>230300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>171500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>74800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>8100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-78500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>222700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>129700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>161300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>192200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>214700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>131200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>148300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>164400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>208200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>104600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>114200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>128200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>140200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3806,251 +3958,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>340500</v>
+      </c>
+      <c r="F35" s="3">
         <v>356700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>230900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>260900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>305100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>393300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>242200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>252600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>313100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>394400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>249500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>300100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>347100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>340800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>274600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>295700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>331400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>289400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>215300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>250900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>230300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>171500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>74800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>8100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-78500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>222700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>129700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>161300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>192200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>214700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>131200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>148300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>164400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>208200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>104600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>114200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>128200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>140200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44044</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43953</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43862</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43771</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43680</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43589</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43498</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43407</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43316</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43134</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43036</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42945</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42854</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42763</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4092,8 +4262,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4135,139 +4307,147 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>158500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>166300</v>
+      </c>
+      <c r="F41" s="3">
         <v>424200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>204900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>242700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>454600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>703200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>177800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>414000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>524600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>766600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>121800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>388600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>636400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>737900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>250600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>434200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>654500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>431600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>605100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>770100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>947500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1046100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>560900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1157300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1043500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>392300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>208800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>177400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>326800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>409300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>296900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>237100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>231900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>277400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>46800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>92900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>321700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>385000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>55000</v>
+      </c>
+      <c r="F42" s="3">
         <v>70000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -4322,535 +4502,565 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC42" s="3">
         <v>110000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>110000</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF42" s="3">
         <v>150000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>195000</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="3">
-        <v>0</v>
-      </c>
       <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>149000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>237200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>120000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>60000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>180000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>150000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>30000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AQ42" s="3">
         <v>110000</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>248200</v>
+      </c>
+      <c r="F43" s="3">
         <v>296200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>237400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>224400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>225100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>223300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>213600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>200900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>203500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>207900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>202900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>174400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>190300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>199400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>200300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>180500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>192800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>233700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>169200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>154400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>154300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>193100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>136300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>128000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>88700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>139300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>112900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>107300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>110000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>136200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>102400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>103700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>100300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>99700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>82900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>67600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>62900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>88600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>65700</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2406700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2386400</v>
+      </c>
+      <c r="F44" s="3">
         <v>2225500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2743600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2407100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2121500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2013600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2365200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1998300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1906000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1780000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2321300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1815500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1751200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1603500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>2114700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1666100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1570600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1499200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1916300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1443700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1353600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1168200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1439100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1368500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1340600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1293700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1616900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1316000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1250000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1214300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>1484600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>1219700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>1136800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>1096400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>1349700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>1144700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>1048400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>944000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>1137000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>103500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>26500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>28900</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>68700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>62800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>53600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>54400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>28800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>30100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>168600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>180200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>162000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>114100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>116700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>143100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>126700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>108400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>107400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>108700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>145300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>146000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>120000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>158800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>169900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>137400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>155100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>142100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>120700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>96500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>100200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>106900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>107300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>89900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>88600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3068500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3021600</v>
+      </c>
+      <c r="F46" s="3">
         <v>3144100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3370800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3069000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2939700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3028800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2954900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2798700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2760600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2836500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2792000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2519200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2686000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2709300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2745800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2442900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2531900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2281200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2833700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2494900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2563800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2514800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2245000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>2799200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>2728800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>2055300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>2097500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1920600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>2019300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1914900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>2026000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>1830200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>1802700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>1693700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>1646300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>1592500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>1673000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>1536200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>1538500</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4890,11 +5100,11 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4968,226 +5178,238 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3292200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3270000</v>
+      </c>
+      <c r="F48" s="3">
         <v>3247100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3077300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3014700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2910100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2849200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2883500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2825600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2757400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2756900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2696200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2622300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2579500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2570500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2524000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2421300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2397600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2396700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2373200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2379700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2448100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2500400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2552300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2626100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2731800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>2743100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>2762900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>2719500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>2685100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1226000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1257800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1213000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>1191000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>1189500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>1172700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>1095100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>1020900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>1004400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>1001900</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>423300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>426200</v>
+      </c>
+      <c r="F49" s="3">
         <v>429700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>398700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>398100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>10900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>11100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>11200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>11200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>11300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>11400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>11500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>11600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>11900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>12200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>11700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>11900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>12200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>12400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>12600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>12900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>13100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>13300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>13600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>13800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>14000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>14300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>14500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>14700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>15000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>15200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>16100</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5200,14 +5422,20 @@
       <c r="AM49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO49" s="3">
+      <c r="AN49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5325,8 +5553,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5444,127 +5678,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>179900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>177400</v>
+      </c>
+      <c r="F52" s="3">
         <v>114800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>165500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>148900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>126000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>73300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>109000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>101900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>102600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>62600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>95300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>95600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>98300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>78400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>50000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>69900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>70400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>74100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>68200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>67100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>62600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>61400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>60100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>58100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>55900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>51200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>54000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>55500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>47000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>35100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>32900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>30200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>25500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>15900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>14600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>13800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>11300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5682,127 +5928,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6964000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6895200</v>
+      </c>
+      <c r="F54" s="3">
         <v>6999300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7012300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6630600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5986700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6001700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5958500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5737400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5631900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5707000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5595000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5248800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5375700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5370400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5331500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>4946000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5012000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>4764400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5287800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>4954600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5087500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5090000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>4871000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>5497100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>5530600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>4863900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>4928800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>4710400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>4766400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>3191200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>3332700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>3073300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>3022200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>2908700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>2834900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>2702200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>2707600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>2551900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>2551200</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5844,8 +6102,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5887,172 +6147,180 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>646200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>713800</v>
+      </c>
+      <c r="F57" s="3">
         <v>685900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>759000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>708700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>537500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>563800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>593200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>566900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>463800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>544000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>597400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>521300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>621300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>559500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>647100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>586900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>585500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>552700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>747500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>535300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>552800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>477100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>478500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>398000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>466000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>414000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>595000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>450100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>407300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>404000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>574500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>409800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>372700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>325800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>447300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>313500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>319400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>259500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>425100</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>652200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>454500</v>
+      </c>
+      <c r="F58" s="3">
         <v>369000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>842400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>571700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>285800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>288100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>484700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>281300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>284800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>283800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>483200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>287400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>288100</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6125,291 +6393,309 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>542400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>673800</v>
+      </c>
+      <c r="F59" s="3">
         <v>652000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>463000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>460200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>593600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>561000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>405000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>395000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>491400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>490200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>350900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>354300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>415900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1122200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1050700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>915200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1014200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1005300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>876700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>846300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>969900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>866700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>751800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>663300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>630100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>723300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>661900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>614800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>638300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>419700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>409600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>348900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>372400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>316400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>267400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>256800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>264900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>269800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>229600</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2281300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2304100</v>
+      </c>
+      <c r="F60" s="3">
         <v>2224300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2538400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2200800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1763900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1779500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1816400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1591200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1572700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1658200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1836900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1491200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1633900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1681800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1697800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1502100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1599700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1558000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1624100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1381500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1522800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1343700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1230300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1061300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1096200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1137300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1256900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1064900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>1045600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>823700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>984100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>758800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>745100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>642200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>714700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>570300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>584300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>529300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>654600</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1871800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1813100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1732200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1716100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1689400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1635100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1656300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1647700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1608000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1627300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1616700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1593000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1610300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -6435,17 +6721,17 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>800000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>800000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -6482,127 +6768,139 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F62" s="3">
         <v>59600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>63400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>60700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>57100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>56100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>65000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>61900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>61000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>56300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>55900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>56700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>56000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1728800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1711500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1674900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1666700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1671000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1676900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1693200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1720100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1746700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1786200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1865000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1880400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1824500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1824800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1806000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1779200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>547200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>512900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>502100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>493700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>492300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>504100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>496600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>481700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>472300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>444500</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6720,8 +7018,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6839,8 +7143,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6958,127 +7268,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4320200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4314300</v>
+      </c>
+      <c r="F66" s="3">
         <v>4195800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4379300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4026800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3556400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3513300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3629500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3389200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3331200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3427700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3566500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3196900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3357700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3410600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3409300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3176900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3266400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3229000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3301000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3074800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3242800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>3090400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>3016600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>3726300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3776600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2961800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>3081700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2870900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2824800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1371000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1497000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1260900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>1238800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>1134500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>1218800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>1066900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>1065900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>1001700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>1099100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7120,8 +7442,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7239,8 +7563,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7358,8 +7688,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7477,8 +7813,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7596,127 +7938,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1568300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1522400</v>
+      </c>
+      <c r="F72" s="3">
         <v>1736900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1577700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1571600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1420200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1473900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1330200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1355000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1314700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1286800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1051900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1083900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1059300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>995800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>983100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>846000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>851900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>653400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1123700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1034800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1027400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1189400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1059800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>985000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>977000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1128500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1079900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1078700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1188300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1105900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1128000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>1115800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>1094800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>1093500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>943100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>970100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>982400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>905800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>812800</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7834,8 +8188,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7953,8 +8313,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8072,127 +8438,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2643700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2581000</v>
+      </c>
+      <c r="F76" s="3">
         <v>2803500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2633000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2603900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2430300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2488400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2329000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2348200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2300700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2279300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2028500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2051900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2018100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1959800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1922300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1769100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1745600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1535400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1986800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1879800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1844700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1999500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1854400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1770800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1754000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1902100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1847200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1839500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1941600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1820200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>1835700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>1812500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>1783400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>1774200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>1616100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>1635400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>1641700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>1550200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>1452100</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8310,251 +8688,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44044</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43953</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43862</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43771</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43680</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43589</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43498</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43407</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43316</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43134</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43036</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42945</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42854</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42763</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>340500</v>
+      </c>
+      <c r="F81" s="3">
         <v>356700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>230900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>260900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>305100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>393300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>242200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>252600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>313100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>394400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>249500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>300100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>347100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>340800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>274600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>295700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>331400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>289400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>215300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>250900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>230300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>171500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>74800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>8100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-78500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>222700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>129700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>161300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>192200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>214700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>131200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>148300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>164400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>208200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>104600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>114200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>128200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>140200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>87600</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8596,127 +8992,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>71800</v>
+      </c>
+      <c r="F83" s="3">
         <v>69700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>67000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>65300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>64700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>61700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>61400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>61900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>57900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>58200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>58500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>60900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>62800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>59200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>58500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>60900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>62800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>63700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>65200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>69000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>70600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>71400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>72400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>77400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>76600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>76400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>74300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>73100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>71800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>71800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>69800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>69000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>68800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>65000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>62100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>63100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>62500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>59300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8834,8 +9238,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8953,8 +9363,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9072,8 +9488,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9191,8 +9613,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9310,127 +9738,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>119700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>261900</v>
+      </c>
+      <c r="F89" s="3">
         <v>1180600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>96500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>220000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1036600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-56800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>199500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>159300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1118300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-70800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>123900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>304900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>908500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>32800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>114400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>426300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>644400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>13400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>71300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>330100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>551300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>243100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>40300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-24300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>543800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>110200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>175700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>271700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>413900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>154200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>110700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>277300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>450300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>109100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>44200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>175700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>311700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>103400</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9472,127 +9912,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-81300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-58300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-191600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-87300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-77000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-79000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-73900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-114200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-95300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-91000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-124200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-106300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-95000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-109800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-108200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-83500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-49400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-71100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-63800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-51100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-22700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-34600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-35100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-39700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-41500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-57400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-89900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-79400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-63000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-114700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-67400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-74300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-103100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-144400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-116500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-76800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-92500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-131600</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9710,8 +10158,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9829,127 +10283,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-48200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-275800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-95600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-473500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-86400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-76400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-115300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-97800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-93600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-125500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-109500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-96400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-110100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-107600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-85300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-49900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-71900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-68100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-51100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-22700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-34600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-35100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-39900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>73200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-46900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-186600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>49700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-279600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-65100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>20700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>20800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-191500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-163100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-24400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-146500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-196800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-12500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-131600</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9991,8 +10457,10 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10032,11 +10500,11 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10110,8 +10578,14 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10229,8 +10703,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10348,8 +10828,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10467,127 +10953,139 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-471400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-685700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>52100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>165100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-382200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-434700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-64100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-212400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-307800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-347900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-86600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-275400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-296200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-313700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-131100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-284700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-131500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-749800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-127400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-225900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-394000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-799400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>722500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-173700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-128400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-270100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-74500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-236500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-115000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-126300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-131400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-56500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-130700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-126700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-42300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-47200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-32800</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10627,11 +11125,11 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10649,10 +11147,10 @@
         <v>0</v>
       </c>
       <c r="W101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y101" s="3">
         <v>-100</v>
@@ -10663,11 +11161,11 @@
       <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC101" s="3" t="s">
-        <v>8</v>
+      <c r="AB101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-100</v>
       </c>
       <c r="AD101" s="3" t="s">
         <v>8</v>
@@ -10681,11 +11179,11 @@
       <c r="AG101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>0</v>
+      <c r="AH101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ101" s="3">
         <v>0</v>
@@ -10705,123 +11203,135 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-257900</v>
+      </c>
+      <c r="F102" s="3">
         <v>219300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-37800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-211900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-248600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>525400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-236200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-110600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-242000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>644800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-266800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-247800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-101400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>487200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-183600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-220300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>222900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-173500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-165100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-177300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-98600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>485100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-596400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>113800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>651200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>183500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>31400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-149400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-82400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>112300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>59800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>5200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-45600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>230700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-46100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-228900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-63300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>251900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>-61000</v>
       </c>
     </row>
